--- a/examples/Example 2 - 3D/data/example_data.xlsx
+++ b/examples/Example 2 - 3D/data/example_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\00105295\Projects\loopflopy\examples\Example 2 - 3D\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0316C8-1BD7-4D13-9F4F-D9E7A7DA2E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A9D0BB5-129B-4585-9351-6BAC83219207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="18460" windowHeight="11020" tabRatio="1000" activeTab="1" xr2:uid="{BEB68924-1CF9-4A8C-BED3-3B7C03CCF6FB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="18460" windowHeight="11020" tabRatio="1000" activeTab="2" xr2:uid="{BEB68924-1CF9-4A8C-BED3-3B7C03CCF6FB}"/>
   </bookViews>
   <sheets>
     <sheet name="strat" sheetId="22" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="42">
   <si>
     <t>Easting</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>id</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -240,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -307,6 +310,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -998,7 +1007,8 @@
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.26953125" style="6" customWidth="1"/>
-    <col min="2" max="4" width="13.26953125" style="5" customWidth="1"/>
+    <col min="2" max="3" width="11.08984375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="5" customWidth="1"/>
     <col min="5" max="5" width="30.7265625" style="8" customWidth="1"/>
     <col min="6" max="7" width="8.7265625" style="5" customWidth="1"/>
     <col min="8" max="8" width="9.1796875" style="5" bestFit="1" customWidth="1"/>
@@ -1098,8 +1108,8 @@
       <c r="I3" s="12">
         <v>300</v>
       </c>
-      <c r="J3" s="12">
-        <v>150</v>
+      <c r="J3" s="24" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -1124,14 +1134,14 @@
       <c r="G4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="25">
         <v>0</v>
       </c>
       <c r="I4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="16" t="s">
-        <v>14</v>
+      <c r="J4" s="25" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
